--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104674_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104674_W24.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4998</v>
+        <v>4.4116</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2079</v>
+        <v>6.4928</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7081</v>
+        <v>-2.0812</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6253</v>
+        <v>4.6285</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7994</v>
+        <v>2.7975</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8259</v>
+        <v>1.831</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4419</v>
+        <v>6.4187</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7924</v>
+        <v>3.7749</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6495</v>
+        <v>2.6438</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8166</v>
+        <v>-1.7902</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4889</v>
+        <v>0.3962</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8075</v>
+        <v>0.1228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6814</v>
+        <v>0.2733</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8689</v>
+        <v>2.863</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6209</v>
+        <v>3.0586</v>
       </c>
       <c r="F3" t="n">
-        <v>0.248</v>
+        <v>-0.1955</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9906</v>
+        <v>3.6024</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5283</v>
+        <v>0.0713</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5189</v>
+        <v>3.5311</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9573</v>
+        <v>3.4558</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0866</v>
+        <v>0.1724</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8707</v>
+        <v>3.2834</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9666</v>
+        <v>0.1467</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6149</v>
+        <v>-0.1011</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3517</v>
+        <v>0.2477</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.398</v>
+        <v>-0.5816</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0907</v>
+        <v>-0.3485</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3073</v>
+        <v>-0.2331</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5122</v>
+        <v>2.7868</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9551</v>
+        <v>2.3868</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4429</v>
+        <v>0.4001</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6096</v>
+        <v>2.0029</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0619</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5477</v>
+        <v>2.5205</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4835</v>
+        <v>2.9458</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1732</v>
+        <v>0.0862</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3104</v>
+        <v>2.8596</v>
       </c>
       <c r="M4" t="n">
-        <v>0.126</v>
+        <v>-0.9428</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1113</v>
+        <v>-0.6037</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2373</v>
+        <v>-0.3391</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1233</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1.1342</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.1342</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.9367</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.4869</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.4497</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.1607</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.0927</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-1.2534</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2315</v>
+        <v>0.4572</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2978</v>
+        <v>2.7525</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0663</v>
+        <v>-2.2954</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8475</v>
+        <v>0.5622</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9118000000000001</v>
+        <v>1.0566</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9356</v>
+        <v>-0.4944</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9604</v>
+        <v>3.2551</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7317</v>
+        <v>2.0339</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2287</v>
+        <v>1.2211</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.113</v>
+        <v>-2.6929</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8198</v>
+        <v>-0.9774</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2931</v>
+        <v>-1.7155</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0281</v>
+        <v>-0.1231</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4869</v>
+        <v>0.1623</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4588</v>
+        <v>-0.2854</v>
       </c>
       <c r="V5" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.0927</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.0927</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2006</v>
+        <v>0.3907</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7109</v>
+        <v>1.6464</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5103</v>
+        <v>-1.2557</v>
       </c>
       <c r="G6" t="n">
-        <v>0.552</v>
+        <v>1.8573</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0504</v>
+        <v>0.9187</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4984</v>
+        <v>0.9386</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2721</v>
+        <v>2.9448</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0434</v>
+        <v>1.7237</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2287</v>
+        <v>1.2211</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7202</v>
+        <v>-1.0876</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.993</v>
+        <v>-0.805</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7272</v>
+        <v>-0.2826</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3799</v>
+        <v>0.1269</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>-0.1116</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4706</v>
+        <v>0.2385</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4822</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4822</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5423</v>
+        <v>-0.0786</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0806</v>
+        <v>1.2733</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6229</v>
+        <v>-1.3519</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3865</v>
+        <v>1.1999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.821</v>
+        <v>0.6979</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4345</v>
+        <v>0.502</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9104</v>
+        <v>3.0887</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2468</v>
+        <v>1.5029</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6636</v>
+        <v>1.5858</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5239</v>
+        <v>-1.8888</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4258</v>
+        <v>-0.805</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P7" t="n">
+        <v>-1.3658</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-2.2763</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.4575</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.0838</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.3736</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1.1342</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.1342</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1639</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.6956</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.8595</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.0927</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.0927</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.121</v>
+        <v>-0.4904</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6984</v>
+        <v>0.4782</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8193</v>
+        <v>-0.9685</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1981</v>
+        <v>0.3876</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6969</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5011</v>
+        <v>-0.4365</v>
       </c>
       <c r="J8" t="n">
-        <v>3.116</v>
+        <v>1.8883</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5168</v>
+        <v>1.2411</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5992</v>
+        <v>0.6473</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9179</v>
+        <v>-1.5007</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8198</v>
+        <v>-0.4169</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5044</v>
+        <v>0.2115</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6956</v>
+        <v>-0.272</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8087</v>
+        <v>0.4835</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3607</v>
+        <v>-1.2821</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1165</v>
+        <v>-0.3033</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7558</v>
+        <v>-0.9788</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4832</v>
+        <v>0.5482</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2034</v>
+        <v>0.7035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2798</v>
+        <v>-0.1553</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8547</v>
+        <v>1.1346</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9666</v>
+        <v>1.1204</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.0142</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.5865</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2368</v>
+        <v>-0.4169</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3918</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3247</v>
+        <v>0.0999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2994</v>
+        <v>-0.2998</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0253</v>
+        <v>0.3997</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3856</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3214</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5937</v>
+        <v>-1.9554</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4663</v>
+        <v>-2.422</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1274</v>
+        <v>0.4666</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5531</v>
+        <v>-1.4784</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6998</v>
+        <v>-1.2061</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1467</v>
+        <v>-0.2723</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1548</v>
+        <v>-0.8643</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1256</v>
+        <v>-0.976</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0292</v>
+        <v>0.1117</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6017</v>
+        <v>-0.6141</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4258</v>
+        <v>-0.2301</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1759</v>
+        <v>-0.384</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2129</v>
+        <v>0.7294</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4869</v>
+        <v>0.0161</v>
       </c>
       <c r="U10" t="n">
-        <v>0.274</v>
+        <v>0.7134</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9541</v>
+        <v>-3.3267</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5917</v>
+        <v>-1.214</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3624</v>
+        <v>-2.1126</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1022</v>
+        <v>0.0992</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1155</v>
+        <v>0.1095</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0133</v>
+        <v>-0.0103</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6174</v>
+        <v>2.5908</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9036</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5152</v>
+        <v>-2.4916</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5858</v>
+        <v>0.0569</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>-0.3417</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1793</v>
+        <v>0.3986</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.741200000000001</v>
+        <v>3.776099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>13.3971</v>
+        <v>14.1493</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.6558</v>
+        <v>-10.3729</v>
       </c>
       <c r="G12" t="n">
-        <v>13.3817</v>
+        <v>13.4098</v>
       </c>
       <c r="H12" t="n">
-        <v>5.425</v>
+        <v>5.455399999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>7.956499999999998</v>
+        <v>7.954400000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>27.0591</v>
+        <v>26.8583</v>
       </c>
       <c r="K12" t="n">
-        <v>11.6535</v>
+        <v>11.5651</v>
       </c>
       <c r="L12" t="n">
-        <v>15.4059</v>
+        <v>15.2932</v>
       </c>
       <c r="M12" t="n">
-        <v>-13.6776</v>
+        <v>-13.4485</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.2282</v>
+        <v>-6.1096</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.449400000000001</v>
+        <v>-7.339</v>
       </c>
       <c r="P12" t="n">
-        <v>-10.2075</v>
+        <v>-10.2434</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.1468</v>
+        <v>-18.2107</v>
       </c>
       <c r="R12" t="n">
-        <v>7.939200000000001</v>
+        <v>7.9672</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2723000000000002</v>
+        <v>0.7676000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3288</v>
+        <v>-1.2795</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0566</v>
+        <v>2.0473</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1607000000000002</v>
+        <v>-0.1578000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>6.813499999999999</v>
+        <v>6.781</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.9741</v>
+        <v>-6.9386</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0708</v>
+        <v>4.7867</v>
       </c>
       <c r="E13" t="n">
-        <v>4.836</v>
+        <v>4.7997</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2348</v>
+        <v>-0.0129</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7978</v>
+        <v>1.7919</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8963</v>
+        <v>1.8793</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0985</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6094</v>
+        <v>3.5809</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8257</v>
+        <v>2.7989</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8116</v>
+        <v>-1.789</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4564</v>
+        <v>0.1754</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1875</v>
+        <v>-0.1862</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6439</v>
+        <v>0.3616</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.871</v>
+        <v>3.3223</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6111</v>
+        <v>2.2135</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2599</v>
+        <v>1.1087</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.3829</v>
+        <v>-3.393</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6694</v>
+        <v>-0.6774</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.7135</v>
+        <v>-2.7157</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4945</v>
+        <v>-0.529</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7477</v>
+        <v>0.7305</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2423</v>
+        <v>-1.2595</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8884</v>
+        <v>-2.864</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4171</v>
+        <v>-1.4078</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4712</v>
+        <v>-1.4562</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0271</v>
+        <v>0.4877</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5989</v>
+        <v>0.2481</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4282</v>
+        <v>0.2396</v>
       </c>
       <c r="V14" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1369</v>
+        <v>2.1216</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6601</v>
+        <v>3.232</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5232</v>
+        <v>-1.1104</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1861</v>
+        <v>-1.1721</v>
       </c>
       <c r="H15" t="n">
-        <v>0.645</v>
+        <v>0.6462</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8311</v>
+        <v>-1.8183</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7499</v>
+        <v>2.7352</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5585</v>
+        <v>1.5513</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1914</v>
+        <v>1.1839</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.9361</v>
+        <v>-3.9073</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.0225</v>
+        <v>-3.0022</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2648</v>
+        <v>-0.2998</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1825</v>
+        <v>-0.5927</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0823</v>
+        <v>0.2929</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.14</v>
+        <v>0.3928</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1514</v>
+        <v>2.6244</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0114</v>
+        <v>-2.2317</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5483</v>
+        <v>1.3348</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7056</v>
+        <v>1.2294</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1573</v>
+        <v>0.1054</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1302</v>
+        <v>3.6292</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9493</v>
+        <v>2.982</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0795</v>
+        <v>0.6473</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6785</v>
+        <v>-2.2945</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7563</v>
+        <v>-1.7526</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9222</v>
+        <v>-0.5419</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1004</v>
+        <v>-0.6249</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0212</v>
+        <v>-0.4114</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.2135</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0505</v>
+        <v>0.2798</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3064</v>
+        <v>0.0179</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2559</v>
+        <v>0.2619</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3469</v>
+        <v>-1.5481</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2323</v>
+        <v>-1.706</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1145</v>
+        <v>0.1579</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6594</v>
+        <v>0.1134</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9958</v>
+        <v>-0.9588</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6636</v>
+        <v>1.0722</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3125</v>
+        <v>-1.6615</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7635</v>
+        <v>-0.7472</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.549</v>
+        <v>-0.9143</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9769</v>
+        <v>0.2345</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7652</v>
+        <v>-0.0955</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2117</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.8353</v>
       </c>
       <c r="E18" t="n">
-        <v>0.483</v>
+        <v>0.344</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2385</v>
+        <v>-1.1792</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1521</v>
+        <v>-1.1536</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.925</v>
+        <v>-1.9189</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7729</v>
+        <v>0.7653</v>
       </c>
       <c r="J18" t="n">
-        <v>0.225</v>
+        <v>0.2094</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3771</v>
+        <v>-1.3629</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4231</v>
+        <v>0.3379</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2994</v>
+        <v>0.1833</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1237</v>
+        <v>0.1546</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1116</v>
+        <v>-2.0733</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1254</v>
+        <v>2.3768</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.237</v>
+        <v>-4.4501</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2745</v>
+        <v>-1.2864</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1729</v>
+        <v>-2.1877</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8983</v>
+        <v>0.9014</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3674</v>
+        <v>3.3277</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0631</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>3.4304</v>
+        <v>3.4181</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.6419</v>
+        <v>-4.6141</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.1098</v>
+        <v>-2.0973</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5321</v>
+        <v>-2.5168</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7585</v>
+        <v>-0.1998</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5293</v>
+        <v>-0.1769</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2292</v>
+        <v>-0.0229</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4102</v>
+        <v>-2.4082</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7081</v>
+        <v>-2.1606</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.09</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1945</v>
+        <v>-2.0706</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6279</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2062</v>
+        <v>-1.2117</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5784</v>
+        <v>0.5702</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7701</v>
+        <v>2.7371</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L20" t="n">
-        <v>3.425</v>
+        <v>3.4028</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.398</v>
+        <v>-3.3786</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.8467</v>
+        <v>-2.8326</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6512</v>
+        <v>-0.0849</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9739</v>
+        <v>-0.5021</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3227</v>
+        <v>0.4171</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6563</v>
+        <v>-3.9911</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.107</v>
+        <v>-1.5859</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5493</v>
+        <v>-2.4051</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6285</v>
+        <v>-3.6229</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.8045</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.8175</v>
+        <v>-2.8184</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3369</v>
+        <v>-1.3442</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2917</v>
+        <v>-2.2788</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2256</v>
+        <v>-0.1209</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2299</v>
+        <v>-0.2418</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0042</v>
+        <v>0.1209</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7789</v>
+        <v>-4.5737</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8969</v>
+        <v>-3.5594</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.882</v>
+        <v>-1.0142</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7259</v>
+        <v>-3.7188</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0174</v>
+        <v>-3.0149</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0025</v>
+        <v>-1.0111</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3463</v>
+        <v>0.3447</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3488</v>
+        <v>-1.3559</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7234</v>
+        <v>-2.7077</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0549</v>
+        <v>-1.0487</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1739</v>
+        <v>0.3728</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8</v>
+        <v>0.6448</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7412</v>
+        <v>-2.7308</v>
       </c>
       <c r="E23" t="n">
-        <v>10.6559</v>
+        <v>10.373</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.3971</v>
+        <v>-13.1036</v>
       </c>
       <c r="G23" t="n">
-        <v>-13.3815</v>
+        <v>-13.4098</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.4251</v>
+        <v>-5.4552</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.9566</v>
+        <v>-7.9545</v>
       </c>
       <c r="J23" t="n">
-        <v>13.6775</v>
+        <v>13.4486</v>
       </c>
       <c r="K23" t="n">
-        <v>6.2282</v>
+        <v>6.1097</v>
       </c>
       <c r="L23" t="n">
-        <v>7.449299999999998</v>
+        <v>7.338900000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-27.0592</v>
+        <v>-26.8584</v>
       </c>
       <c r="N23" t="n">
-        <v>-11.6533</v>
+        <v>-11.565</v>
       </c>
       <c r="O23" t="n">
-        <v>-15.4056</v>
+        <v>-15.2935</v>
       </c>
       <c r="P23" t="n">
-        <v>10.2075</v>
+        <v>10.2433</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7.9392</v>
+        <v>-7.9672</v>
       </c>
       <c r="R23" t="n">
-        <v>18.1467</v>
+        <v>18.2105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2720999999999998</v>
+        <v>0.278</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.0565</v>
+        <v>-2.0472</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3287</v>
+        <v>2.3251</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1607</v>
+        <v>0.1578000000000003</v>
       </c>
       <c r="W23" t="n">
-        <v>6.9741</v>
+        <v>6.9388</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.8134</v>
+        <v>-6.781</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104674_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104674_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.9386</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104674_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-6.781</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
